--- a/src/data/results.xlsx
+++ b/src/data/results.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -742,16 +742,7453 @@
         <v>Completed</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-02-06T21:33:54.721Z</v>
+      </c>
+      <c r="B10" t="str">
+        <v>session-1770413523199</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E10" t="str">
+        <v>1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Error: sessionsAPI is not defined</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-02-06T21:33:54.721Z</v>
+      </c>
+      <c r="B11" t="str">
+        <v>session-1770413523199</v>
+      </c>
+      <c r="C11" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J11" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K11" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Error: sessionsAPI is not defined</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>2026-02-06T21:33:54.721Z</v>
+      </c>
+      <c r="B12" t="str">
+        <v>session-1770413523199</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E12" t="str">
+        <v>3</v>
+      </c>
+      <c r="F12" t="str">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J12" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K12" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: Timeout 30000ms exceeded.
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>2026-02-06T21:33:54.721Z</v>
+      </c>
+      <c r="B13" t="str">
+        <v>session-1770413523199</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E13" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F13" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J13" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K13" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: Timeout 30000ms exceeded.
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>2026-02-06T21:33:54.721Z</v>
+      </c>
+      <c r="B14" t="str">
+        <v>session-1770413523199</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E14" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F14" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J14" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K14" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: Timeout 30000ms exceeded.
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-02-06T22:07:35.428Z</v>
+      </c>
+      <c r="B15" t="str">
+        <v>session-1770415484735</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E15" t="str">
+        <v>1</v>
+      </c>
+      <c r="F15" t="str">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>6</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J15" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K15" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-02-06T22:07:35.428Z</v>
+      </c>
+      <c r="B16" t="str">
+        <v>session-1770415484735</v>
+      </c>
+      <c r="C16" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J16" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K16" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-02-06T22:07:35.428Z</v>
+      </c>
+      <c r="B17" t="str">
+        <v>session-1770415484735</v>
+      </c>
+      <c r="C17" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E17" t="str">
+        <v>3</v>
+      </c>
+      <c r="F17" t="str">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-02-06T22:07:35.428Z</v>
+      </c>
+      <c r="B18" t="str">
+        <v>session-1770415484735</v>
+      </c>
+      <c r="C18" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E18" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F18" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J18" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K18" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-02-06T22:07:35.428Z</v>
+      </c>
+      <c r="B19" t="str">
+        <v>session-1770415484735</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E19" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F19" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G19">
+        <v>6</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J19" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K19" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-02-07T03:02:47.634Z</v>
+      </c>
+      <c r="B20" t="str">
+        <v>session-1770433317006</v>
+      </c>
+      <c r="C20" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J20" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K20" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Error: invalid input syntax for type uuid: "1"</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-02-07T03:02:47.634Z</v>
+      </c>
+      <c r="B21" t="str">
+        <v>session-1770433317006</v>
+      </c>
+      <c r="C21" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J21" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K21" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Error: invalid input syntax for type uuid: "2"</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-02-07T03:02:47.634Z</v>
+      </c>
+      <c r="B22" t="str">
+        <v>session-1770433317006</v>
+      </c>
+      <c r="C22" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E22" t="str">
+        <v>3</v>
+      </c>
+      <c r="F22" t="str">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J22" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K22" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Error: invalid input syntax for type uuid: "3"</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-02-07T03:02:47.634Z</v>
+      </c>
+      <c r="B23" t="str">
+        <v>session-1770433317006</v>
+      </c>
+      <c r="C23" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E23" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F23" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J23" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K23" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Error: invalid input syntax for type uuid: "SUDB-004"</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-02-07T03:02:47.634Z</v>
+      </c>
+      <c r="B24" t="str">
+        <v>session-1770433317006</v>
+      </c>
+      <c r="C24" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E24" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F24" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J24" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K24" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Error: invalid input syntax for type uuid: "CALG-001"</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-02-07T03:07:58.017Z</v>
+      </c>
+      <c r="B25" t="str">
+        <v>session-1770433633327</v>
+      </c>
+      <c r="C25" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E25" t="str">
+        <v>1</v>
+      </c>
+      <c r="F25" t="str">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J25" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K25" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Error: invalid input syntax for type uuid: "1"</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-02-07T03:07:58.017Z</v>
+      </c>
+      <c r="B26" t="str">
+        <v>session-1770433633327</v>
+      </c>
+      <c r="C26" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J26" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K26" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Error: invalid input syntax for type uuid: "2"</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-02-07T03:07:58.017Z</v>
+      </c>
+      <c r="B27" t="str">
+        <v>session-1770433633327</v>
+      </c>
+      <c r="C27" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E27" t="str">
+        <v>3</v>
+      </c>
+      <c r="F27" t="str">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J27" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K27" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Error: invalid input syntax for type uuid: "3"</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-02-07T03:07:58.017Z</v>
+      </c>
+      <c r="B28" t="str">
+        <v>session-1770433633327</v>
+      </c>
+      <c r="C28" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E28" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F28" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J28" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K28" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Error: invalid input syntax for type uuid: "CALG-001"</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-02-07T03:07:58.017Z</v>
+      </c>
+      <c r="B29" t="str">
+        <v>session-1770433633327</v>
+      </c>
+      <c r="C29" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E29" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F29" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J29" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K29" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Error: invalid input syntax for type uuid: "SUDB-004"</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-02-07T03:10:14.325Z</v>
+      </c>
+      <c r="B30" t="str">
+        <v>session-1770433763118</v>
+      </c>
+      <c r="C30" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E30" t="str">
+        <v>1</v>
+      </c>
+      <c r="F30" t="str">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J30" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K30" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Error: invalid input syntax for type uuid: "1"</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-02-07T03:10:14.325Z</v>
+      </c>
+      <c r="B31" t="str">
+        <v>session-1770433763118</v>
+      </c>
+      <c r="C31" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J31" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K31" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Error: invalid input syntax for type uuid: "2"</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-02-07T03:10:14.325Z</v>
+      </c>
+      <c r="B32" t="str">
+        <v>session-1770433763118</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E32" t="str">
+        <v>3</v>
+      </c>
+      <c r="F32" t="str">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J32" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K32" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Error: invalid input syntax for type uuid: "3"</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-02-07T03:10:14.325Z</v>
+      </c>
+      <c r="B33" t="str">
+        <v>session-1770433763118</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E33" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F33" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Error: invalid input syntax for type uuid: "SUDB-004"</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-02-07T03:10:14.325Z</v>
+      </c>
+      <c r="B34" t="str">
+        <v>session-1770433763118</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E34" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F34" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Error: invalid input syntax for type uuid: "CALG-001"</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-02-07T03:30:42.019Z</v>
+      </c>
+      <c r="B35" t="str">
+        <v>session-1770434998998</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E35" t="str">
+        <v>1</v>
+      </c>
+      <c r="F35" t="str">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Error: invalid input syntax for type uuid: "1"</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-02-07T03:30:42.019Z</v>
+      </c>
+      <c r="B36" t="str">
+        <v>session-1770434998998</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E36" t="str">
+        <v>2</v>
+      </c>
+      <c r="F36" t="str">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J36" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K36" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Error: invalid input syntax for type uuid: "2"</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-02-07T03:30:42.019Z</v>
+      </c>
+      <c r="B37" t="str">
+        <v>session-1770434998998</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E37" t="str">
+        <v>3</v>
+      </c>
+      <c r="F37" t="str">
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J37" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K37" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Error: invalid input syntax for type uuid: "3"</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-02-07T03:30:42.019Z</v>
+      </c>
+      <c r="B38" t="str">
+        <v>session-1770434998998</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E38" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F38" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J38" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K38" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Error: invalid input syntax for type uuid: "CALG-001"</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-02-07T03:30:42.019Z</v>
+      </c>
+      <c r="B39" t="str">
+        <v>session-1770434998998</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E39" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F39" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J39" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K39" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Error: invalid input syntax for type uuid: "SUDB-004"</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-02-07T03:34:00.314Z</v>
+      </c>
+      <c r="B40" t="str">
+        <v>session-1770435127797</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E40" t="str">
+        <v>1</v>
+      </c>
+      <c r="F40" t="str">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J40" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K40" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Error: invalid input syntax for type uuid: "1"</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-02-07T03:34:00.314Z</v>
+      </c>
+      <c r="B41" t="str">
+        <v>session-1770435127797</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E41" t="str">
+        <v>2</v>
+      </c>
+      <c r="F41" t="str">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J41" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K41" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Error: invalid input syntax for type uuid: "2"</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-02-07T03:34:00.314Z</v>
+      </c>
+      <c r="B42" t="str">
+        <v>session-1770435127797</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E42" t="str">
+        <v>3</v>
+      </c>
+      <c r="F42" t="str">
+        <v>3</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J42" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K42" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Error: fetch failed</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-02-07T03:34:00.314Z</v>
+      </c>
+      <c r="B43" t="str">
+        <v>session-1770435127797</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E43" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F43" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J43" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K43" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Error: invalid input syntax for type uuid: "SUDB-004"</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-02-07T03:34:00.314Z</v>
+      </c>
+      <c r="B44" t="str">
+        <v>session-1770435127797</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E44" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F44" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J44" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K44" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Error: invalid input syntax for type uuid: "CALG-001"</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-02-07T03:37:21.469Z</v>
+      </c>
+      <c r="B45" t="str">
+        <v>session-1770435271085</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E45" t="str">
+        <v>1</v>
+      </c>
+      <c r="F45" t="str">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>6</v>
+      </c>
+      <c r="H45">
+        <v>6</v>
+      </c>
+      <c r="I45" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J45" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K45" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-02-07T03:37:21.469Z</v>
+      </c>
+      <c r="B46" t="str">
+        <v>session-1770435271085</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E46" t="str">
+        <v>2</v>
+      </c>
+      <c r="F46" t="str">
+        <v>2</v>
+      </c>
+      <c r="G46">
+        <v>6</v>
+      </c>
+      <c r="H46">
+        <v>6</v>
+      </c>
+      <c r="I46" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J46" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K46" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-02-07T03:37:21.469Z</v>
+      </c>
+      <c r="B47" t="str">
+        <v>session-1770435271085</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E47" t="str">
+        <v>3</v>
+      </c>
+      <c r="F47" t="str">
+        <v>3</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+      <c r="H47">
+        <v>5</v>
+      </c>
+      <c r="I47" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J47" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K47" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-02-07T03:37:21.469Z</v>
+      </c>
+      <c r="B48" t="str">
+        <v>session-1770435271085</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E48" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F48" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G48">
+        <v>6</v>
+      </c>
+      <c r="H48">
+        <v>6</v>
+      </c>
+      <c r="I48" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J48" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K48" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-02-07T03:37:21.469Z</v>
+      </c>
+      <c r="B49" t="str">
+        <v>session-1770435271085</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E49" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F49" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G49">
+        <v>5</v>
+      </c>
+      <c r="H49">
+        <v>5</v>
+      </c>
+      <c r="I49" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J49" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K49" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-02-07T03:54:14.287Z</v>
+      </c>
+      <c r="B50" t="str">
+        <v>session-1770436254837</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E50" t="str">
+        <v>1</v>
+      </c>
+      <c r="F50" t="str">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+      <c r="H50">
+        <v>5</v>
+      </c>
+      <c r="I50" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J50" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K50" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-02-07T03:54:14.287Z</v>
+      </c>
+      <c r="B51" t="str">
+        <v>session-1770436254837</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2</v>
+      </c>
+      <c r="F51" t="str">
+        <v>2</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
+      </c>
+      <c r="H51">
+        <v>6</v>
+      </c>
+      <c r="I51" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J51" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K51" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-02-07T03:54:14.287Z</v>
+      </c>
+      <c r="B52" t="str">
+        <v>session-1770436254837</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E52" t="str">
+        <v>3</v>
+      </c>
+      <c r="F52" t="str">
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <v>6</v>
+      </c>
+      <c r="H52">
+        <v>6</v>
+      </c>
+      <c r="I52" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J52" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K52" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-02-07T03:54:14.287Z</v>
+      </c>
+      <c r="B53" t="str">
+        <v>session-1770436254837</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E53" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F53" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G53">
+        <v>5</v>
+      </c>
+      <c r="H53">
+        <v>5</v>
+      </c>
+      <c r="I53" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J53" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K53" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-02-07T03:54:14.287Z</v>
+      </c>
+      <c r="B54" t="str">
+        <v>session-1770436254837</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E54" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F54" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G54">
+        <v>5</v>
+      </c>
+      <c r="H54">
+        <v>5</v>
+      </c>
+      <c r="I54" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J54" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K54" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-02-07T04:08:04.015Z</v>
+      </c>
+      <c r="B55" t="str">
+        <v>session-1770437207357</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E55" t="str">
+        <v>1</v>
+      </c>
+      <c r="F55" t="str">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J55" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K55" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Error: GameSession is not defined</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-02-07T04:08:04.015Z</v>
+      </c>
+      <c r="B56" t="str">
+        <v>session-1770437207357</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2</v>
+      </c>
+      <c r="F56" t="str">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J56" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K56" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Error: page.goto: Target page, context or browser has been closed</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-02-07T04:08:04.015Z</v>
+      </c>
+      <c r="B57" t="str">
+        <v>session-1770437207357</v>
+      </c>
+      <c r="C57" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E57" t="str">
+        <v>3</v>
+      </c>
+      <c r="F57" t="str">
+        <v>3</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J57" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K57" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Error: GameSession is not defined</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-02-07T04:08:04.015Z</v>
+      </c>
+      <c r="B58" t="str">
+        <v>session-1770437207357</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E58" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F58" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J58" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K58" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Error: GameSession is not defined</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-02-07T04:08:04.015Z</v>
+      </c>
+      <c r="B59" t="str">
+        <v>session-1770437207357</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E59" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F59" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J59" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K59" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Error: GameSession is not defined</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-02-07T04:33:26.603Z</v>
+      </c>
+      <c r="B60" t="str">
+        <v>session-1770438629652</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E60" t="str">
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>5</v>
+      </c>
+      <c r="H60">
+        <v>5</v>
+      </c>
+      <c r="I60" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J60" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K60" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-02-07T04:33:26.603Z</v>
+      </c>
+      <c r="B61" t="str">
+        <v>session-1770438629652</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E61" t="str">
+        <v>2</v>
+      </c>
+      <c r="F61" t="str">
+        <v>2</v>
+      </c>
+      <c r="G61">
+        <v>5</v>
+      </c>
+      <c r="H61">
+        <v>5</v>
+      </c>
+      <c r="I61" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J61" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K61" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L61" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-02-07T04:33:26.603Z</v>
+      </c>
+      <c r="B62" t="str">
+        <v>session-1770438629652</v>
+      </c>
+      <c r="C62" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E62" t="str">
+        <v>3</v>
+      </c>
+      <c r="F62" t="str">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>5</v>
+      </c>
+      <c r="H62">
+        <v>5</v>
+      </c>
+      <c r="I62" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-02-07T04:33:26.603Z</v>
+      </c>
+      <c r="B63" t="str">
+        <v>session-1770438629652</v>
+      </c>
+      <c r="C63" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E63" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F63" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G63">
+        <v>6</v>
+      </c>
+      <c r="H63">
+        <v>6</v>
+      </c>
+      <c r="I63" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J63" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K63" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-02-07T04:33:26.603Z</v>
+      </c>
+      <c r="B64" t="str">
+        <v>session-1770438629652</v>
+      </c>
+      <c r="C64" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E64" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F64" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G64">
+        <v>5</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J64" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K64" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-02-07T04:51:05.901Z</v>
+      </c>
+      <c r="B65" t="str">
+        <v>session-1770439669146</v>
+      </c>
+      <c r="C65" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E65" t="str">
+        <v>1</v>
+      </c>
+      <c r="F65" t="str">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>6</v>
+      </c>
+      <c r="H65">
+        <v>6</v>
+      </c>
+      <c r="I65" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-02-07T04:51:05.901Z</v>
+      </c>
+      <c r="B66" t="str">
+        <v>session-1770439669146</v>
+      </c>
+      <c r="C66" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E66" t="str">
+        <v>2</v>
+      </c>
+      <c r="F66" t="str">
+        <v>2</v>
+      </c>
+      <c r="G66">
+        <v>5</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J66" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K66" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-02-07T04:51:05.901Z</v>
+      </c>
+      <c r="B67" t="str">
+        <v>session-1770439669146</v>
+      </c>
+      <c r="C67" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E67" t="str">
+        <v>3</v>
+      </c>
+      <c r="F67" t="str">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <v>5</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J67" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K67" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-02-07T04:51:05.901Z</v>
+      </c>
+      <c r="B68" t="str">
+        <v>session-1770439669146</v>
+      </c>
+      <c r="C68" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E68" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F68" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G68">
+        <v>6</v>
+      </c>
+      <c r="H68">
+        <v>6</v>
+      </c>
+      <c r="I68" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J68" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K68" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-02-07T04:51:05.901Z</v>
+      </c>
+      <c r="B69" t="str">
+        <v>session-1770439669146</v>
+      </c>
+      <c r="C69" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E69" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F69" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G69">
+        <v>5</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-02-07T05:19:23.611Z</v>
+      </c>
+      <c r="B70" t="str">
+        <v>session-1770441518345</v>
+      </c>
+      <c r="C70" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E70" t="str">
+        <v>1</v>
+      </c>
+      <c r="F70" t="str">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Error: players is not defined</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-02-07T05:19:23.611Z</v>
+      </c>
+      <c r="B71" t="str">
+        <v>session-1770441518345</v>
+      </c>
+      <c r="C71" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>2</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Error: players is not defined</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-02-07T05:19:23.611Z</v>
+      </c>
+      <c r="B72" t="str">
+        <v>session-1770441518345</v>
+      </c>
+      <c r="C72" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E72" t="str">
+        <v>3</v>
+      </c>
+      <c r="F72" t="str">
+        <v>3</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Error: players is not defined</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-02-07T05:19:23.611Z</v>
+      </c>
+      <c r="B73" t="str">
+        <v>session-1770441518345</v>
+      </c>
+      <c r="C73" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E73" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F73" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Error: players is not defined</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-02-07T05:19:23.611Z</v>
+      </c>
+      <c r="B74" t="str">
+        <v>session-1770441518345</v>
+      </c>
+      <c r="C74" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E74" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F74" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J74" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K74" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Error: players is not defined</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-02-07T05:27:04.850Z</v>
+      </c>
+      <c r="B75" t="str">
+        <v>session-1770441983627</v>
+      </c>
+      <c r="C75" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E75" t="str">
+        <v>1</v>
+      </c>
+      <c r="F75" t="str">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Error: No players in session</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-02-07T05:27:04.850Z</v>
+      </c>
+      <c r="B76" t="str">
+        <v>session-1770441983627</v>
+      </c>
+      <c r="C76" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E76" t="str">
+        <v>2</v>
+      </c>
+      <c r="F76" t="str">
+        <v>2</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Error: No players in session</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-02-07T05:27:04.850Z</v>
+      </c>
+      <c r="B77" t="str">
+        <v>session-1770441983627</v>
+      </c>
+      <c r="C77" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E77" t="str">
+        <v>3</v>
+      </c>
+      <c r="F77" t="str">
+        <v>3</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Error: No players in session</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-02-07T05:27:04.850Z</v>
+      </c>
+      <c r="B78" t="str">
+        <v>session-1770441983627</v>
+      </c>
+      <c r="C78" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E78" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F78" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Error: No players in session</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-02-07T05:27:04.850Z</v>
+      </c>
+      <c r="B79" t="str">
+        <v>session-1770441983627</v>
+      </c>
+      <c r="C79" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E79" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F79" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Error: No players in session</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-02-07T05:28:48.607Z</v>
+      </c>
+      <c r="B80" t="str">
+        <v>session-1770442080450</v>
+      </c>
+      <c r="C80" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E80" t="str">
+        <v>1</v>
+      </c>
+      <c r="F80" t="str">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Error: count is not defined</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-02-07T05:28:48.607Z</v>
+      </c>
+      <c r="B81" t="str">
+        <v>session-1770442080450</v>
+      </c>
+      <c r="C81" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E81" t="str">
+        <v>2</v>
+      </c>
+      <c r="F81" t="str">
+        <v>2</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Error: count is not defined</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-02-07T05:28:48.607Z</v>
+      </c>
+      <c r="B82" t="str">
+        <v>session-1770442080450</v>
+      </c>
+      <c r="C82" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E82" t="str">
+        <v>3</v>
+      </c>
+      <c r="F82" t="str">
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Error: count is not defined</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-02-07T05:28:48.607Z</v>
+      </c>
+      <c r="B83" t="str">
+        <v>session-1770442080450</v>
+      </c>
+      <c r="C83" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E83" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F83" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Error: count is not defined</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-02-07T05:28:48.607Z</v>
+      </c>
+      <c r="B84" t="str">
+        <v>session-1770442080450</v>
+      </c>
+      <c r="C84" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E84" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F84" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Error: count is not defined</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-02-07T05:31:46.118Z</v>
+      </c>
+      <c r="B85" t="str">
+        <v>session-1770442257096</v>
+      </c>
+      <c r="C85" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E85" t="str">
+        <v>1</v>
+      </c>
+      <c r="F85" t="str">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Error: A is not defined</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2026-02-07T05:31:46.118Z</v>
+      </c>
+      <c r="B86" t="str">
+        <v>session-1770442257096</v>
+      </c>
+      <c r="C86" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E86" t="str">
+        <v>2</v>
+      </c>
+      <c r="F86" t="str">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Error: A is not defined</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2026-02-07T05:31:46.118Z</v>
+      </c>
+      <c r="B87" t="str">
+        <v>session-1770442257096</v>
+      </c>
+      <c r="C87" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E87" t="str">
+        <v>3</v>
+      </c>
+      <c r="F87" t="str">
+        <v>3</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Error: A is not defined</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2026-02-07T05:31:46.118Z</v>
+      </c>
+      <c r="B88" t="str">
+        <v>session-1770442257096</v>
+      </c>
+      <c r="C88" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E88" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F88" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Error: A is not defined</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2026-02-07T05:31:46.118Z</v>
+      </c>
+      <c r="B89" t="str">
+        <v>session-1770442257096</v>
+      </c>
+      <c r="C89" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E89" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F89" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Error: A is not defined</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2026-02-07T05:36:25.032Z</v>
+      </c>
+      <c r="B90" t="str">
+        <v>session-1770442405946</v>
+      </c>
+      <c r="C90" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E90" t="str">
+        <v>1</v>
+      </c>
+      <c r="F90" t="str">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>5</v>
+      </c>
+      <c r="H90">
+        <v>5</v>
+      </c>
+      <c r="I90" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J90" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K90" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2026-02-07T05:36:25.032Z</v>
+      </c>
+      <c r="B91" t="str">
+        <v>session-1770442405946</v>
+      </c>
+      <c r="C91" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E91" t="str">
+        <v>2</v>
+      </c>
+      <c r="F91" t="str">
+        <v>2</v>
+      </c>
+      <c r="G91">
+        <v>7</v>
+      </c>
+      <c r="H91">
+        <v>7</v>
+      </c>
+      <c r="I91" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J91" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K91" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2026-02-07T05:36:25.032Z</v>
+      </c>
+      <c r="B92" t="str">
+        <v>session-1770442405946</v>
+      </c>
+      <c r="C92" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E92" t="str">
+        <v>3</v>
+      </c>
+      <c r="F92" t="str">
+        <v>3</v>
+      </c>
+      <c r="G92">
+        <v>5</v>
+      </c>
+      <c r="H92">
+        <v>5</v>
+      </c>
+      <c r="I92" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2026-02-07T05:36:25.032Z</v>
+      </c>
+      <c r="B93" t="str">
+        <v>session-1770442405946</v>
+      </c>
+      <c r="C93" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E93" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F93" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G93">
+        <v>5</v>
+      </c>
+      <c r="H93">
+        <v>5</v>
+      </c>
+      <c r="I93" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2026-02-07T05:36:25.032Z</v>
+      </c>
+      <c r="B94" t="str">
+        <v>session-1770442405946</v>
+      </c>
+      <c r="C94" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E94" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F94" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G94">
+        <v>6</v>
+      </c>
+      <c r="H94">
+        <v>6</v>
+      </c>
+      <c r="I94" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2026-02-07T05:45:33.509Z</v>
+      </c>
+      <c r="B95" t="str">
+        <v>session-1770442953576</v>
+      </c>
+      <c r="C95" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E95" t="str">
+        <v>1</v>
+      </c>
+      <c r="F95" t="str">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>6</v>
+      </c>
+      <c r="H95">
+        <v>6</v>
+      </c>
+      <c r="I95" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2026-02-07T05:45:33.509Z</v>
+      </c>
+      <c r="B96" t="str">
+        <v>session-1770442953576</v>
+      </c>
+      <c r="C96" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E96" t="str">
+        <v>2</v>
+      </c>
+      <c r="F96" t="str">
+        <v>2</v>
+      </c>
+      <c r="G96">
+        <v>5</v>
+      </c>
+      <c r="H96">
+        <v>5</v>
+      </c>
+      <c r="I96" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2026-02-07T05:45:33.509Z</v>
+      </c>
+      <c r="B97" t="str">
+        <v>session-1770442953576</v>
+      </c>
+      <c r="C97" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E97" t="str">
+        <v>3</v>
+      </c>
+      <c r="F97" t="str">
+        <v>3</v>
+      </c>
+      <c r="G97">
+        <v>5</v>
+      </c>
+      <c r="H97">
+        <v>5</v>
+      </c>
+      <c r="I97" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J97" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K97" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>2026-02-07T05:45:33.509Z</v>
+      </c>
+      <c r="B98" t="str">
+        <v>session-1770442953576</v>
+      </c>
+      <c r="C98" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E98" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F98" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G98">
+        <v>5</v>
+      </c>
+      <c r="H98">
+        <v>5</v>
+      </c>
+      <c r="I98" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J98" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K98" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2026-02-07T05:45:33.509Z</v>
+      </c>
+      <c r="B99" t="str">
+        <v>session-1770442953576</v>
+      </c>
+      <c r="C99" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E99" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F99" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G99">
+        <v>5</v>
+      </c>
+      <c r="H99">
+        <v>5</v>
+      </c>
+      <c r="I99" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J99" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K99" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>2026-02-07T05:56:16.927Z</v>
+      </c>
+      <c r="B100" t="str">
+        <v>session-1770443590794</v>
+      </c>
+      <c r="C100" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E100" t="str">
+        <v>1</v>
+      </c>
+      <c r="F100" t="str">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>6</v>
+      </c>
+      <c r="H100">
+        <v>6</v>
+      </c>
+      <c r="I100" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>2026-02-07T05:56:16.927Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>session-1770443590794</v>
+      </c>
+      <c r="C101" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E101" t="str">
+        <v>2</v>
+      </c>
+      <c r="F101" t="str">
+        <v>2</v>
+      </c>
+      <c r="G101">
+        <v>6</v>
+      </c>
+      <c r="H101">
+        <v>6</v>
+      </c>
+      <c r="I101" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J101" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K101" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>2026-02-07T05:56:16.927Z</v>
+      </c>
+      <c r="B102" t="str">
+        <v>session-1770443590794</v>
+      </c>
+      <c r="C102" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E102" t="str">
+        <v>3</v>
+      </c>
+      <c r="F102" t="str">
+        <v>3</v>
+      </c>
+      <c r="G102">
+        <v>6</v>
+      </c>
+      <c r="H102">
+        <v>6</v>
+      </c>
+      <c r="I102" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J102" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K102" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2026-02-07T05:56:16.927Z</v>
+      </c>
+      <c r="B103" t="str">
+        <v>session-1770443590794</v>
+      </c>
+      <c r="C103" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E103" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F103" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="J103" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K103" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>2026-02-07T05:56:16.927Z</v>
+      </c>
+      <c r="B104" t="str">
+        <v>session-1770443590794</v>
+      </c>
+      <c r="C104" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E104" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F104" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G104">
+        <v>5</v>
+      </c>
+      <c r="H104">
+        <v>5</v>
+      </c>
+      <c r="I104" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L104" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>2026-02-07T06:07:04.178Z</v>
+      </c>
+      <c r="B105" t="str">
+        <v>session-1770444195520</v>
+      </c>
+      <c r="C105" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E105" t="str">
+        <v>1</v>
+      </c>
+      <c r="F105" t="str">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>6</v>
+      </c>
+      <c r="H105">
+        <v>6</v>
+      </c>
+      <c r="I105" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L105" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>2026-02-07T06:07:04.178Z</v>
+      </c>
+      <c r="B106" t="str">
+        <v>session-1770444195520</v>
+      </c>
+      <c r="C106" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E106" t="str">
+        <v>2</v>
+      </c>
+      <c r="F106" t="str">
+        <v>2</v>
+      </c>
+      <c r="G106">
+        <v>6</v>
+      </c>
+      <c r="H106">
+        <v>6</v>
+      </c>
+      <c r="I106" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J106" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K106" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L106" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2026-02-07T06:07:04.178Z</v>
+      </c>
+      <c r="B107" t="str">
+        <v>session-1770444195520</v>
+      </c>
+      <c r="C107" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E107" t="str">
+        <v>3</v>
+      </c>
+      <c r="F107" t="str">
+        <v>3</v>
+      </c>
+      <c r="G107">
+        <v>6</v>
+      </c>
+      <c r="H107">
+        <v>6</v>
+      </c>
+      <c r="I107" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L107" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>2026-02-07T06:07:04.178Z</v>
+      </c>
+      <c r="B108" t="str">
+        <v>session-1770444195520</v>
+      </c>
+      <c r="C108" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E108" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F108" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G108">
+        <v>6</v>
+      </c>
+      <c r="H108">
+        <v>6</v>
+      </c>
+      <c r="I108" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J108" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K108" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>2026-02-07T06:07:04.178Z</v>
+      </c>
+      <c r="B109" t="str">
+        <v>session-1770444195520</v>
+      </c>
+      <c r="C109" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E109" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F109" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G109">
+        <v>6</v>
+      </c>
+      <c r="H109">
+        <v>6</v>
+      </c>
+      <c r="I109" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J109" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K109" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L109" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>2026-02-07T06:11:17.252Z</v>
+      </c>
+      <c r="B110" t="str">
+        <v>session-1770444625616</v>
+      </c>
+      <c r="C110" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E110" t="str">
+        <v>1</v>
+      </c>
+      <c r="F110" t="str">
+        <v>1</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J110" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K110" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L110" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>2026-02-07T06:11:17.252Z</v>
+      </c>
+      <c r="B111" t="str">
+        <v>session-1770444625616</v>
+      </c>
+      <c r="C111" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E111" t="str">
+        <v>2</v>
+      </c>
+      <c r="F111" t="str">
+        <v>2</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J111" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K111" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L111" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>2026-02-07T06:11:17.252Z</v>
+      </c>
+      <c r="B112" t="str">
+        <v>session-1770444625616</v>
+      </c>
+      <c r="C112" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E112" t="str">
+        <v>3</v>
+      </c>
+      <c r="F112" t="str">
+        <v>3</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J112" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K112" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L112" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>2026-02-07T06:11:17.252Z</v>
+      </c>
+      <c r="B113" t="str">
+        <v>session-1770444625616</v>
+      </c>
+      <c r="C113" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E113" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F113" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J113" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K113" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L113" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>2026-02-07T06:11:17.252Z</v>
+      </c>
+      <c r="B114" t="str">
+        <v>session-1770444625616</v>
+      </c>
+      <c r="C114" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E114" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F114" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J114" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K114" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L114" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>2026-02-07T06:14:09.218Z</v>
+      </c>
+      <c r="B115" t="str">
+        <v>session-1770444800285</v>
+      </c>
+      <c r="C115" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E115" t="str">
+        <v>1</v>
+      </c>
+      <c r="F115" t="str">
+        <v>1</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J115" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K115" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L115" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>2026-02-07T06:14:09.218Z</v>
+      </c>
+      <c r="B116" t="str">
+        <v>session-1770444800285</v>
+      </c>
+      <c r="C116" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E116" t="str">
+        <v>2</v>
+      </c>
+      <c r="F116" t="str">
+        <v>2</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J116" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K116" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L116" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>2026-02-07T06:14:09.218Z</v>
+      </c>
+      <c r="B117" t="str">
+        <v>session-1770444800285</v>
+      </c>
+      <c r="C117" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E117" t="str">
+        <v>3</v>
+      </c>
+      <c r="F117" t="str">
+        <v>3</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J117" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K117" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L117" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>2026-02-07T06:14:09.218Z</v>
+      </c>
+      <c r="B118" t="str">
+        <v>session-1770444800285</v>
+      </c>
+      <c r="C118" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E118" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F118" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J118" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K118" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L118" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>2026-02-07T06:14:09.218Z</v>
+      </c>
+      <c r="B119" t="str">
+        <v>session-1770444800285</v>
+      </c>
+      <c r="C119" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E119" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F119" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J119" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K119" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L119" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>2026-02-07T06:16:07.075Z</v>
+      </c>
+      <c r="B120" t="str">
+        <v>session-1770444911882</v>
+      </c>
+      <c r="C120" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E120" t="str">
+        <v>1</v>
+      </c>
+      <c r="F120" t="str">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J120" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K120" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L120" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>2026-02-07T06:16:07.075Z</v>
+      </c>
+      <c r="B121" t="str">
+        <v>session-1770444911882</v>
+      </c>
+      <c r="C121" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E121" t="str">
+        <v>2</v>
+      </c>
+      <c r="F121" t="str">
+        <v>2</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J121" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K121" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L121" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>2026-02-07T06:16:07.075Z</v>
+      </c>
+      <c r="B122" t="str">
+        <v>session-1770444911882</v>
+      </c>
+      <c r="C122" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E122" t="str">
+        <v>3</v>
+      </c>
+      <c r="F122" t="str">
+        <v>3</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J122" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K122" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L122" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>2026-02-07T06:16:07.075Z</v>
+      </c>
+      <c r="B123" t="str">
+        <v>session-1770444911882</v>
+      </c>
+      <c r="C123" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E123" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F123" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J123" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K123" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L123" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>2026-02-07T06:16:07.075Z</v>
+      </c>
+      <c r="B124" t="str">
+        <v>session-1770444911882</v>
+      </c>
+      <c r="C124" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E124" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F124" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J124" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K124" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L124" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>2026-02-07T06:20:43.674Z</v>
+      </c>
+      <c r="B125" t="str">
+        <v>session-1770445119743</v>
+      </c>
+      <c r="C125" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E125" t="str">
+        <v>1</v>
+      </c>
+      <c r="F125" t="str">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J125" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K125" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L125" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>2026-02-07T06:20:43.674Z</v>
+      </c>
+      <c r="B126" t="str">
+        <v>session-1770445119743</v>
+      </c>
+      <c r="C126" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E126" t="str">
+        <v>2</v>
+      </c>
+      <c r="F126" t="str">
+        <v>2</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J126" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K126" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L126" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>2026-02-07T06:20:43.674Z</v>
+      </c>
+      <c r="B127" t="str">
+        <v>session-1770445119743</v>
+      </c>
+      <c r="C127" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E127" t="str">
+        <v>3</v>
+      </c>
+      <c r="F127" t="str">
+        <v>3</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J127" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K127" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L127" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>2026-02-07T06:20:43.674Z</v>
+      </c>
+      <c r="B128" t="str">
+        <v>session-1770445119743</v>
+      </c>
+      <c r="C128" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E128" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F128" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J128" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K128" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L128" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>2026-02-07T06:20:43.674Z</v>
+      </c>
+      <c r="B129" t="str">
+        <v>session-1770445119743</v>
+      </c>
+      <c r="C129" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E129" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F129" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L129" t="str">
+        <v>Error: Session not found</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>2026-02-07T06:33:48.611Z</v>
+      </c>
+      <c r="B130" t="str">
+        <v>session-1770445846142</v>
+      </c>
+      <c r="C130" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E130" t="str">
+        <v>1</v>
+      </c>
+      <c r="F130" t="str">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>5</v>
+      </c>
+      <c r="H130">
+        <v>5</v>
+      </c>
+      <c r="I130" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L130" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>2026-02-07T06:33:48.611Z</v>
+      </c>
+      <c r="B131" t="str">
+        <v>session-1770445846142</v>
+      </c>
+      <c r="C131" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E131" t="str">
+        <v>2</v>
+      </c>
+      <c r="F131" t="str">
+        <v>2</v>
+      </c>
+      <c r="G131">
+        <v>6</v>
+      </c>
+      <c r="H131">
+        <v>6</v>
+      </c>
+      <c r="I131" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L131" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>2026-02-07T06:33:48.611Z</v>
+      </c>
+      <c r="B132" t="str">
+        <v>session-1770445846142</v>
+      </c>
+      <c r="C132" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E132" t="str">
+        <v>3</v>
+      </c>
+      <c r="F132" t="str">
+        <v>3</v>
+      </c>
+      <c r="G132">
+        <v>5</v>
+      </c>
+      <c r="H132">
+        <v>5</v>
+      </c>
+      <c r="I132" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L132" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>2026-02-07T06:33:48.611Z</v>
+      </c>
+      <c r="B133" t="str">
+        <v>session-1770445846142</v>
+      </c>
+      <c r="C133" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E133" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F133" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G133">
+        <v>6</v>
+      </c>
+      <c r="H133">
+        <v>6</v>
+      </c>
+      <c r="I133" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L133" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>2026-02-07T06:33:48.611Z</v>
+      </c>
+      <c r="B134" t="str">
+        <v>session-1770445846142</v>
+      </c>
+      <c r="C134" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E134" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F134" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G134">
+        <v>6</v>
+      </c>
+      <c r="H134">
+        <v>6</v>
+      </c>
+      <c r="I134" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L134" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>2026-02-07T06:47:02.152Z</v>
+      </c>
+      <c r="B135" t="str">
+        <v>session-1770446641665</v>
+      </c>
+      <c r="C135" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E135" t="str">
+        <v>1</v>
+      </c>
+      <c r="F135" t="str">
+        <v>1</v>
+      </c>
+      <c r="G135">
+        <v>6</v>
+      </c>
+      <c r="H135">
+        <v>6</v>
+      </c>
+      <c r="I135" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L135" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>2026-02-07T06:47:02.152Z</v>
+      </c>
+      <c r="B136" t="str">
+        <v>session-1770446641665</v>
+      </c>
+      <c r="C136" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E136" t="str">
+        <v>2</v>
+      </c>
+      <c r="F136" t="str">
+        <v>2</v>
+      </c>
+      <c r="G136">
+        <v>6</v>
+      </c>
+      <c r="H136">
+        <v>6</v>
+      </c>
+      <c r="I136" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L136" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>2026-02-07T06:47:02.152Z</v>
+      </c>
+      <c r="B137" t="str">
+        <v>session-1770446641665</v>
+      </c>
+      <c r="C137" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E137" t="str">
+        <v>3</v>
+      </c>
+      <c r="F137" t="str">
+        <v>3</v>
+      </c>
+      <c r="G137">
+        <v>5</v>
+      </c>
+      <c r="H137">
+        <v>5</v>
+      </c>
+      <c r="I137" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L137" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>2026-02-07T06:47:02.152Z</v>
+      </c>
+      <c r="B138" t="str">
+        <v>session-1770446641665</v>
+      </c>
+      <c r="C138" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E138" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F138" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G138">
+        <v>5</v>
+      </c>
+      <c r="H138">
+        <v>5</v>
+      </c>
+      <c r="I138" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J138" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K138" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L138" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>2026-02-07T06:47:02.152Z</v>
+      </c>
+      <c r="B139" t="str">
+        <v>session-1770446641665</v>
+      </c>
+      <c r="C139" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E139" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F139" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G139">
+        <v>5</v>
+      </c>
+      <c r="H139">
+        <v>5</v>
+      </c>
+      <c r="I139" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K139" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L139" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>2026-02-07T06:50:44.159Z</v>
+      </c>
+      <c r="B140" t="str">
+        <v>session-1770446915572</v>
+      </c>
+      <c r="C140" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E140" t="str">
+        <v>1</v>
+      </c>
+      <c r="F140" t="str">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K140" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L140" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>2026-02-07T06:50:44.159Z</v>
+      </c>
+      <c r="B141" t="str">
+        <v>session-1770446915572</v>
+      </c>
+      <c r="C141" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E141" t="str">
+        <v>2</v>
+      </c>
+      <c r="F141" t="str">
+        <v>2</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K141" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L141" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="142" xml:space="preserve">
+      <c r="A142" t="str">
+        <v>2026-02-07T06:50:44.159Z</v>
+      </c>
+      <c r="B142" t="str">
+        <v>session-1770446915572</v>
+      </c>
+      <c r="C142" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E142" t="str">
+        <v>3</v>
+      </c>
+      <c r="F142" t="str">
+        <v>3</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K142" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L142" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: Timeout 30000ms exceeded.
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>2026-02-07T06:50:44.159Z</v>
+      </c>
+      <c r="B143" t="str">
+        <v>session-1770446915572</v>
+      </c>
+      <c r="C143" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E143" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F143" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K143" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L143" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>2026-02-07T06:50:44.159Z</v>
+      </c>
+      <c r="B144" t="str">
+        <v>session-1770446915572</v>
+      </c>
+      <c r="C144" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E144" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F144" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K144" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L144" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>2026-02-07T06:53:55.905Z</v>
+      </c>
+      <c r="B145" t="str">
+        <v>session-1770447054542</v>
+      </c>
+      <c r="C145" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E145" t="str">
+        <v>1</v>
+      </c>
+      <c r="F145" t="str">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>5</v>
+      </c>
+      <c r="H145">
+        <v>5</v>
+      </c>
+      <c r="I145" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K145" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L145" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>2026-02-07T06:53:55.905Z</v>
+      </c>
+      <c r="B146" t="str">
+        <v>session-1770447054542</v>
+      </c>
+      <c r="C146" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E146" t="str">
+        <v>2</v>
+      </c>
+      <c r="F146" t="str">
+        <v>2</v>
+      </c>
+      <c r="G146">
+        <v>5</v>
+      </c>
+      <c r="H146">
+        <v>5</v>
+      </c>
+      <c r="I146" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K146" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L146" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>2026-02-07T06:53:55.905Z</v>
+      </c>
+      <c r="B147" t="str">
+        <v>session-1770447054542</v>
+      </c>
+      <c r="C147" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E147" t="str">
+        <v>3</v>
+      </c>
+      <c r="F147" t="str">
+        <v>3</v>
+      </c>
+      <c r="G147">
+        <v>6</v>
+      </c>
+      <c r="H147">
+        <v>6</v>
+      </c>
+      <c r="I147" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J147" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K147" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L147" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>2026-02-07T06:53:55.905Z</v>
+      </c>
+      <c r="B148" t="str">
+        <v>session-1770447054542</v>
+      </c>
+      <c r="C148" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E148" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F148" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G148">
+        <v>5</v>
+      </c>
+      <c r="H148">
+        <v>5</v>
+      </c>
+      <c r="I148" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K148" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L148" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>2026-02-07T06:53:55.905Z</v>
+      </c>
+      <c r="B149" t="str">
+        <v>session-1770447054542</v>
+      </c>
+      <c r="C149" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E149" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F149" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G149">
+        <v>5</v>
+      </c>
+      <c r="H149">
+        <v>5</v>
+      </c>
+      <c r="I149" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K149" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L149" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>2026-02-07T07:00:54.543Z</v>
+      </c>
+      <c r="B150" t="str">
+        <v>session-1770447389683</v>
+      </c>
+      <c r="C150" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E150" t="str">
+        <v>1</v>
+      </c>
+      <c r="F150" t="str">
+        <v>1</v>
+      </c>
+      <c r="G150">
+        <v>6</v>
+      </c>
+      <c r="H150">
+        <v>6</v>
+      </c>
+      <c r="I150" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K150" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L150" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>2026-02-07T07:00:54.543Z</v>
+      </c>
+      <c r="B151" t="str">
+        <v>session-1770447389683</v>
+      </c>
+      <c r="C151" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E151" t="str">
+        <v>2</v>
+      </c>
+      <c r="F151" t="str">
+        <v>2</v>
+      </c>
+      <c r="G151">
+        <v>10</v>
+      </c>
+      <c r="H151">
+        <v>10</v>
+      </c>
+      <c r="I151" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K151" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L151" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>2026-02-07T07:00:54.543Z</v>
+      </c>
+      <c r="B152" t="str">
+        <v>session-1770447389683</v>
+      </c>
+      <c r="C152" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E152" t="str">
+        <v>3</v>
+      </c>
+      <c r="F152" t="str">
+        <v>3</v>
+      </c>
+      <c r="G152">
+        <v>6</v>
+      </c>
+      <c r="H152">
+        <v>6</v>
+      </c>
+      <c r="I152" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J152" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K152" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L152" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>2026-02-07T07:00:54.543Z</v>
+      </c>
+      <c r="B153" t="str">
+        <v>session-1770447389683</v>
+      </c>
+      <c r="C153" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E153" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F153" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G153">
+        <v>5</v>
+      </c>
+      <c r="H153">
+        <v>5</v>
+      </c>
+      <c r="I153" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K153" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L153" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>2026-02-07T07:00:54.543Z</v>
+      </c>
+      <c r="B154" t="str">
+        <v>session-1770447389683</v>
+      </c>
+      <c r="C154" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E154" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F154" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G154">
+        <v>7</v>
+      </c>
+      <c r="H154">
+        <v>7</v>
+      </c>
+      <c r="I154" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K154" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L154" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>2026-02-07T07:12:43.827Z</v>
+      </c>
+      <c r="B155" t="str">
+        <v>session-1770448188809</v>
+      </c>
+      <c r="C155" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E155" t="str">
+        <v>1</v>
+      </c>
+      <c r="F155" t="str">
+        <v>1</v>
+      </c>
+      <c r="G155">
+        <v>5</v>
+      </c>
+      <c r="H155">
+        <v>5</v>
+      </c>
+      <c r="I155" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J155" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K155" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L155" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>2026-02-07T07:12:43.827Z</v>
+      </c>
+      <c r="B156" t="str">
+        <v>session-1770448188809</v>
+      </c>
+      <c r="C156" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E156" t="str">
+        <v>2</v>
+      </c>
+      <c r="F156" t="str">
+        <v>2</v>
+      </c>
+      <c r="G156">
+        <v>6</v>
+      </c>
+      <c r="H156">
+        <v>6</v>
+      </c>
+      <c r="I156" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K156" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L156" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>2026-02-07T07:12:43.827Z</v>
+      </c>
+      <c r="B157" t="str">
+        <v>session-1770448188809</v>
+      </c>
+      <c r="C157" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E157" t="str">
+        <v>3</v>
+      </c>
+      <c r="F157" t="str">
+        <v>3</v>
+      </c>
+      <c r="G157">
+        <v>5</v>
+      </c>
+      <c r="H157">
+        <v>5</v>
+      </c>
+      <c r="I157" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K157" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L157" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>2026-02-07T07:12:43.827Z</v>
+      </c>
+      <c r="B158" t="str">
+        <v>session-1770448188809</v>
+      </c>
+      <c r="C158" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E158" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F158" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G158">
+        <v>6</v>
+      </c>
+      <c r="H158">
+        <v>6</v>
+      </c>
+      <c r="I158" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K158" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L158" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>2026-02-07T07:12:43.827Z</v>
+      </c>
+      <c r="B159" t="str">
+        <v>session-1770448188809</v>
+      </c>
+      <c r="C159" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E159" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F159" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G159">
+        <v>6</v>
+      </c>
+      <c r="H159">
+        <v>6</v>
+      </c>
+      <c r="I159" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K159" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L159" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>2026-02-07T07:19:33.916Z</v>
+      </c>
+      <c r="B160" t="str">
+        <v>session-1770448590892</v>
+      </c>
+      <c r="C160" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E160" t="str">
+        <v>1</v>
+      </c>
+      <c r="F160" t="str">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <v>6</v>
+      </c>
+      <c r="H160">
+        <v>6</v>
+      </c>
+      <c r="I160" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K160" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L160" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>2026-02-07T07:19:33.916Z</v>
+      </c>
+      <c r="B161" t="str">
+        <v>session-1770448590892</v>
+      </c>
+      <c r="C161" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E161" t="str">
+        <v>2</v>
+      </c>
+      <c r="F161" t="str">
+        <v>2</v>
+      </c>
+      <c r="G161">
+        <v>5</v>
+      </c>
+      <c r="H161">
+        <v>5</v>
+      </c>
+      <c r="I161" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J161" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K161" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L161" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>2026-02-07T07:19:33.916Z</v>
+      </c>
+      <c r="B162" t="str">
+        <v>session-1770448590892</v>
+      </c>
+      <c r="C162" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E162" t="str">
+        <v>3</v>
+      </c>
+      <c r="F162" t="str">
+        <v>3</v>
+      </c>
+      <c r="G162">
+        <v>6</v>
+      </c>
+      <c r="H162">
+        <v>6</v>
+      </c>
+      <c r="I162" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J162" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K162" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L162" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>2026-02-07T07:19:33.916Z</v>
+      </c>
+      <c r="B163" t="str">
+        <v>session-1770448590892</v>
+      </c>
+      <c r="C163" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E163" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F163" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G163">
+        <v>5</v>
+      </c>
+      <c r="H163">
+        <v>5</v>
+      </c>
+      <c r="I163" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J163" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K163" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L163" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>2026-02-07T07:19:33.916Z</v>
+      </c>
+      <c r="B164" t="str">
+        <v>session-1770448590892</v>
+      </c>
+      <c r="C164" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E164" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F164" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G164">
+        <v>6</v>
+      </c>
+      <c r="H164">
+        <v>6</v>
+      </c>
+      <c r="I164" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K164" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L164" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>2026-02-07T07:32:30.848Z</v>
+      </c>
+      <c r="B165" t="str">
+        <v>session-1770449352555</v>
+      </c>
+      <c r="C165" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E165" t="str">
+        <v>1</v>
+      </c>
+      <c r="F165" t="str">
+        <v>1</v>
+      </c>
+      <c r="G165">
+        <v>6</v>
+      </c>
+      <c r="H165">
+        <v>6</v>
+      </c>
+      <c r="I165" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L165" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>2026-02-07T07:32:30.848Z</v>
+      </c>
+      <c r="B166" t="str">
+        <v>session-1770449352555</v>
+      </c>
+      <c r="C166" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E166" t="str">
+        <v>2</v>
+      </c>
+      <c r="F166" t="str">
+        <v>2</v>
+      </c>
+      <c r="G166">
+        <v>7</v>
+      </c>
+      <c r="H166">
+        <v>7</v>
+      </c>
+      <c r="I166" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J166" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K166" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L166" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>2026-02-07T07:32:30.848Z</v>
+      </c>
+      <c r="B167" t="str">
+        <v>session-1770449352555</v>
+      </c>
+      <c r="C167" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E167" t="str">
+        <v>3</v>
+      </c>
+      <c r="F167" t="str">
+        <v>3</v>
+      </c>
+      <c r="G167">
+        <v>5</v>
+      </c>
+      <c r="H167">
+        <v>5</v>
+      </c>
+      <c r="I167" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L167" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>2026-02-07T07:32:30.848Z</v>
+      </c>
+      <c r="B168" t="str">
+        <v>session-1770449352555</v>
+      </c>
+      <c r="C168" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E168" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F168" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G168">
+        <v>7</v>
+      </c>
+      <c r="H168">
+        <v>7</v>
+      </c>
+      <c r="I168" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L168" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>2026-02-07T07:32:30.848Z</v>
+      </c>
+      <c r="B169" t="str">
+        <v>session-1770449352555</v>
+      </c>
+      <c r="C169" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E169" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F169" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G169">
+        <v>6</v>
+      </c>
+      <c r="H169">
+        <v>6</v>
+      </c>
+      <c r="I169" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K169" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L169" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>2026-02-07T07:38:45.245Z</v>
+      </c>
+      <c r="B170" t="str">
+        <v>session-1770449674612</v>
+      </c>
+      <c r="C170" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E170" t="str">
+        <v>1</v>
+      </c>
+      <c r="F170" t="str">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>5</v>
+      </c>
+      <c r="H170">
+        <v>5</v>
+      </c>
+      <c r="I170" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K170" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L170" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>2026-02-07T07:38:45.245Z</v>
+      </c>
+      <c r="B171" t="str">
+        <v>session-1770449674612</v>
+      </c>
+      <c r="C171" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E171" t="str">
+        <v>2</v>
+      </c>
+      <c r="F171" t="str">
+        <v>2</v>
+      </c>
+      <c r="G171">
+        <v>5</v>
+      </c>
+      <c r="H171">
+        <v>5</v>
+      </c>
+      <c r="I171" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K171" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L171" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>2026-02-07T07:38:45.245Z</v>
+      </c>
+      <c r="B172" t="str">
+        <v>session-1770449674612</v>
+      </c>
+      <c r="C172" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E172" t="str">
+        <v>3</v>
+      </c>
+      <c r="F172" t="str">
+        <v>3</v>
+      </c>
+      <c r="G172">
+        <v>5</v>
+      </c>
+      <c r="H172">
+        <v>5</v>
+      </c>
+      <c r="I172" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K172" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L172" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>2026-02-07T07:38:45.245Z</v>
+      </c>
+      <c r="B173" t="str">
+        <v>session-1770449674612</v>
+      </c>
+      <c r="C173" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E173" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F173" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="G173">
+        <v>6</v>
+      </c>
+      <c r="H173">
+        <v>6</v>
+      </c>
+      <c r="I173" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K173" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L173" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>2026-02-07T07:38:45.245Z</v>
+      </c>
+      <c r="B174" t="str">
+        <v>session-1770449674612</v>
+      </c>
+      <c r="C174" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E174" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F174" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="G174">
+        <v>5</v>
+      </c>
+      <c r="H174">
+        <v>5</v>
+      </c>
+      <c r="I174" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K174" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L174" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>2026-02-07T09:36:51.521Z</v>
+      </c>
+      <c r="B175" t="str">
+        <v>session-1770456744166</v>
+      </c>
+      <c r="C175" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E175" t="str">
+        <v>1</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Aiden20</v>
+      </c>
+      <c r="G175">
+        <v>6</v>
+      </c>
+      <c r="H175">
+        <v>6</v>
+      </c>
+      <c r="I175" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K175" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L175" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>2026-02-07T09:36:51.521Z</v>
+      </c>
+      <c r="B176" t="str">
+        <v>session-1770456744166</v>
+      </c>
+      <c r="C176" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E176" t="str">
+        <v>2</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Jayden97</v>
+      </c>
+      <c r="G176">
+        <v>5</v>
+      </c>
+      <c r="H176">
+        <v>5</v>
+      </c>
+      <c r="I176" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J176" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K176" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L176" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>2026-02-07T09:36:51.521Z</v>
+      </c>
+      <c r="B177" t="str">
+        <v>session-1770456744166</v>
+      </c>
+      <c r="C177" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E177" t="str">
+        <v>3</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Maya59</v>
+      </c>
+      <c r="G177">
+        <v>5</v>
+      </c>
+      <c r="H177">
+        <v>5</v>
+      </c>
+      <c r="I177" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J177" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K177" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L177" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>2026-02-07T09:36:51.521Z</v>
+      </c>
+      <c r="B178" t="str">
+        <v>session-1770456744166</v>
+      </c>
+      <c r="C178" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E178" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F178" t="str">
+        <v>Liam74</v>
+      </c>
+      <c r="G178">
+        <v>6</v>
+      </c>
+      <c r="H178">
+        <v>6</v>
+      </c>
+      <c r="I178" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K178" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L178" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>2026-02-07T09:36:51.521Z</v>
+      </c>
+      <c r="B179" t="str">
+        <v>session-1770456744166</v>
+      </c>
+      <c r="C179" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E179" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F179" t="str">
+        <v>Ryder57</v>
+      </c>
+      <c r="G179">
+        <v>6</v>
+      </c>
+      <c r="H179">
+        <v>6</v>
+      </c>
+      <c r="I179" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K179" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L179" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>2026-02-07T09:41:47.348Z</v>
+      </c>
+      <c r="B180" t="str">
+        <v>session-1770457027726</v>
+      </c>
+      <c r="C180" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E180" t="str">
+        <v>1</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Aiden81</v>
+      </c>
+      <c r="G180">
+        <v>5</v>
+      </c>
+      <c r="H180">
+        <v>5</v>
+      </c>
+      <c r="I180" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K180" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L180" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>2026-02-07T09:41:47.348Z</v>
+      </c>
+      <c r="B181" t="str">
+        <v>session-1770457027726</v>
+      </c>
+      <c r="C181" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E181" t="str">
+        <v>2</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Jayden71</v>
+      </c>
+      <c r="G181">
+        <v>5</v>
+      </c>
+      <c r="H181">
+        <v>5</v>
+      </c>
+      <c r="I181" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J181" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K181" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L181" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>2026-02-07T09:41:47.348Z</v>
+      </c>
+      <c r="B182" t="str">
+        <v>session-1770457027726</v>
+      </c>
+      <c r="C182" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E182" t="str">
+        <v>3</v>
+      </c>
+      <c r="F182" t="str">
+        <v>Maya28</v>
+      </c>
+      <c r="G182">
+        <v>5</v>
+      </c>
+      <c r="H182">
+        <v>5</v>
+      </c>
+      <c r="I182" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K182" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L182" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>2026-02-07T09:41:47.348Z</v>
+      </c>
+      <c r="B183" t="str">
+        <v>session-1770457027726</v>
+      </c>
+      <c r="C183" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E183" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F183" t="str">
+        <v>Ryder74</v>
+      </c>
+      <c r="G183">
+        <v>5</v>
+      </c>
+      <c r="H183">
+        <v>5</v>
+      </c>
+      <c r="I183" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K183" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L183" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>2026-02-07T09:41:47.348Z</v>
+      </c>
+      <c r="B184" t="str">
+        <v>session-1770457027726</v>
+      </c>
+      <c r="C184" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E184" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F184" t="str">
+        <v>Liam58</v>
+      </c>
+      <c r="G184">
+        <v>5</v>
+      </c>
+      <c r="H184">
+        <v>5</v>
+      </c>
+      <c r="I184" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K184" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L184" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="185" xml:space="preserve">
+      <c r="A185" t="str">
+        <v>2026-02-07T10:39:02.783Z</v>
+      </c>
+      <c r="B185" t="str">
+        <v>session-1770460643910</v>
+      </c>
+      <c r="C185" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E185" t="str">
+        <v>1</v>
+      </c>
+      <c r="F185" t="str">
+        <v>Aiden57</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K185" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L185" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: net::ERR_NAME_NOT_RESOLVED at https://www.crowd.live/FNJCN
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="186" xml:space="preserve">
+      <c r="A186" t="str">
+        <v>2026-02-07T10:39:02.783Z</v>
+      </c>
+      <c r="B186" t="str">
+        <v>session-1770460643910</v>
+      </c>
+      <c r="C186" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E186" t="str">
+        <v>2</v>
+      </c>
+      <c r="F186" t="str">
+        <v>Jayden7</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K186" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L186" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: net::ERR_NAME_NOT_RESOLVED at https://www.crowd.live/FNJCN
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="187" xml:space="preserve">
+      <c r="A187" t="str">
+        <v>2026-02-07T10:39:02.783Z</v>
+      </c>
+      <c r="B187" t="str">
+        <v>session-1770460643910</v>
+      </c>
+      <c r="C187" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E187" t="str">
+        <v>3</v>
+      </c>
+      <c r="F187" t="str">
+        <v>Maya7</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K187" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L187" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: net::ERR_NAME_NOT_RESOLVED at https://www.crowd.live/FNJCN
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="188" xml:space="preserve">
+      <c r="A188" t="str">
+        <v>2026-02-07T10:39:02.783Z</v>
+      </c>
+      <c r="B188" t="str">
+        <v>session-1770460643910</v>
+      </c>
+      <c r="C188" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E188" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F188" t="str">
+        <v>Liam27</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K188" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L188" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: net::ERR_NAME_NOT_RESOLVED at https://www.crowd.live/FNJCN
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="189" xml:space="preserve">
+      <c r="A189" t="str">
+        <v>2026-02-07T10:39:02.783Z</v>
+      </c>
+      <c r="B189" t="str">
+        <v>session-1770460643910</v>
+      </c>
+      <c r="C189" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E189" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F189" t="str">
+        <v>Ryder33</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K189" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L189" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: page.goto: net::ERR_NAME_NOT_RESOLVED at https://www.crowd.live/FNJCN
+Call log:
+_x001b_[2m  - navigating to "https://www.crowd.live/FNJCN", waiting until "networkidle"_x001b_[22m
+</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>2026-02-07T23:36:58.426Z</v>
+      </c>
+      <c r="B190" t="str">
+        <v>session-1770507190458</v>
+      </c>
+      <c r="C190" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E190" t="str">
+        <v>1</v>
+      </c>
+      <c r="F190" t="str">
+        <v>Aiden38</v>
+      </c>
+      <c r="G190">
+        <v>5</v>
+      </c>
+      <c r="H190">
+        <v>5</v>
+      </c>
+      <c r="I190" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J190" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K190" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L190" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>2026-02-07T23:36:58.426Z</v>
+      </c>
+      <c r="B191" t="str">
+        <v>session-1770507190458</v>
+      </c>
+      <c r="C191" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E191" t="str">
+        <v>2</v>
+      </c>
+      <c r="F191" t="str">
+        <v>Jayden2</v>
+      </c>
+      <c r="G191">
+        <v>6</v>
+      </c>
+      <c r="H191">
+        <v>6</v>
+      </c>
+      <c r="I191" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J191" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K191" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L191" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>2026-02-07T23:36:58.426Z</v>
+      </c>
+      <c r="B192" t="str">
+        <v>session-1770507190458</v>
+      </c>
+      <c r="C192" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E192" t="str">
+        <v>3</v>
+      </c>
+      <c r="F192" t="str">
+        <v>Maya50</v>
+      </c>
+      <c r="G192">
+        <v>6</v>
+      </c>
+      <c r="H192">
+        <v>6</v>
+      </c>
+      <c r="I192" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J192" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K192" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L192" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>2026-02-07T23:36:58.426Z</v>
+      </c>
+      <c r="B193" t="str">
+        <v>session-1770507190458</v>
+      </c>
+      <c r="C193" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E193" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F193" t="str">
+        <v>Ryder80</v>
+      </c>
+      <c r="G193">
+        <v>6</v>
+      </c>
+      <c r="H193">
+        <v>6</v>
+      </c>
+      <c r="I193" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J193" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K193" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>2026-02-07T23:36:58.426Z</v>
+      </c>
+      <c r="B194" t="str">
+        <v>session-1770507190458</v>
+      </c>
+      <c r="C194" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E194" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F194" t="str">
+        <v>Liam9</v>
+      </c>
+      <c r="G194">
+        <v>6</v>
+      </c>
+      <c r="H194">
+        <v>6</v>
+      </c>
+      <c r="I194" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J194" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K194" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>2026-02-08T03:23:09.769Z</v>
+      </c>
+      <c r="B195" t="str">
+        <v>session-1770520775844</v>
+      </c>
+      <c r="C195" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E195" t="str">
+        <v>1</v>
+      </c>
+      <c r="F195" t="str">
+        <v>Aiden71</v>
+      </c>
+      <c r="G195">
+        <v>5</v>
+      </c>
+      <c r="H195">
+        <v>5</v>
+      </c>
+      <c r="I195" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J195" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K195" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>2026-02-08T03:23:09.769Z</v>
+      </c>
+      <c r="B196" t="str">
+        <v>session-1770520775844</v>
+      </c>
+      <c r="C196" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E196" t="str">
+        <v>2</v>
+      </c>
+      <c r="F196" t="str">
+        <v>Jayden62</v>
+      </c>
+      <c r="G196">
+        <v>6</v>
+      </c>
+      <c r="H196">
+        <v>6</v>
+      </c>
+      <c r="I196" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J196" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K196" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>2026-02-08T03:23:09.769Z</v>
+      </c>
+      <c r="B197" t="str">
+        <v>session-1770520775844</v>
+      </c>
+      <c r="C197" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E197" t="str">
+        <v>3</v>
+      </c>
+      <c r="F197" t="str">
+        <v>Maya43</v>
+      </c>
+      <c r="G197">
+        <v>5</v>
+      </c>
+      <c r="H197">
+        <v>5</v>
+      </c>
+      <c r="I197" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J197" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K197" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>2026-02-08T03:23:09.769Z</v>
+      </c>
+      <c r="B198" t="str">
+        <v>session-1770520775844</v>
+      </c>
+      <c r="C198" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E198" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F198" t="str">
+        <v>Ryder24</v>
+      </c>
+      <c r="G198">
+        <v>5</v>
+      </c>
+      <c r="H198">
+        <v>5</v>
+      </c>
+      <c r="I198" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J198" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K198" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>2026-02-08T03:23:09.769Z</v>
+      </c>
+      <c r="B199" t="str">
+        <v>session-1770520775844</v>
+      </c>
+      <c r="C199" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E199" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F199" t="str">
+        <v>Liam1</v>
+      </c>
+      <c r="G199">
+        <v>5</v>
+      </c>
+      <c r="H199">
+        <v>5</v>
+      </c>
+      <c r="I199" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J199" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K199" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>2026-02-08T04:22:03.068Z</v>
+      </c>
+      <c r="B200" t="str">
+        <v>session-1770524343381</v>
+      </c>
+      <c r="C200" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E200" t="str">
+        <v>1</v>
+      </c>
+      <c r="F200" t="str">
+        <v>Aiden81</v>
+      </c>
+      <c r="G200">
+        <v>5</v>
+      </c>
+      <c r="H200">
+        <v>5</v>
+      </c>
+      <c r="I200" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J200" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K200" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>2026-02-08T04:22:03.068Z</v>
+      </c>
+      <c r="B201" t="str">
+        <v>session-1770524343381</v>
+      </c>
+      <c r="C201" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E201" t="str">
+        <v>2</v>
+      </c>
+      <c r="F201" t="str">
+        <v>Jayden10</v>
+      </c>
+      <c r="G201">
+        <v>6</v>
+      </c>
+      <c r="H201">
+        <v>6</v>
+      </c>
+      <c r="I201" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J201" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K201" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>2026-02-08T04:22:03.068Z</v>
+      </c>
+      <c r="B202" t="str">
+        <v>session-1770524343381</v>
+      </c>
+      <c r="C202" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E202" t="str">
+        <v>3</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Maya67</v>
+      </c>
+      <c r="G202">
+        <v>5</v>
+      </c>
+      <c r="H202">
+        <v>5</v>
+      </c>
+      <c r="I202" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J202" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K202" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>2026-02-08T04:22:03.068Z</v>
+      </c>
+      <c r="B203" t="str">
+        <v>session-1770524343381</v>
+      </c>
+      <c r="C203" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E203" t="str">
+        <v>SUDB-004</v>
+      </c>
+      <c r="F203" t="str">
+        <v>Liam48</v>
+      </c>
+      <c r="G203">
+        <v>5</v>
+      </c>
+      <c r="H203">
+        <v>5</v>
+      </c>
+      <c r="I203" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J203" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K203" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>2026-02-08T04:22:03.068Z</v>
+      </c>
+      <c r="B204" t="str">
+        <v>session-1770524343381</v>
+      </c>
+      <c r="C204" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E204" t="str">
+        <v>CALG-001</v>
+      </c>
+      <c r="F204" t="str">
+        <v>Ryder69</v>
+      </c>
+      <c r="G204">
+        <v>5</v>
+      </c>
+      <c r="H204">
+        <v>5</v>
+      </c>
+      <c r="I204" t="str">
+        <v>100.0</v>
+      </c>
+      <c r="J204" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K204" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Completed</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -893,9 +8330,1374 @@
         <v>100.0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-02-06T21:33:54.736Z</v>
+      </c>
+      <c r="B5" t="str">
+        <v>session-1770413523199</v>
+      </c>
+      <c r="C5" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E5" t="str">
+        <v>111.5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-02-06T22:07:35.438Z</v>
+      </c>
+      <c r="B6" t="str">
+        <v>session-1770415484735</v>
+      </c>
+      <c r="C6" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E6" t="str">
+        <v>170.7</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>27</v>
+      </c>
+      <c r="J6">
+        <v>27</v>
+      </c>
+      <c r="K6" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-02-07T03:02:47.644Z</v>
+      </c>
+      <c r="B7" t="str">
+        <v>session-1770433317006</v>
+      </c>
+      <c r="C7" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E7" t="str">
+        <v>50.6</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-02-07T03:07:58.027Z</v>
+      </c>
+      <c r="B8" t="str">
+        <v>session-1770433633327</v>
+      </c>
+      <c r="C8" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E8" t="str">
+        <v>44.7</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-02-07T03:10:14.334Z</v>
+      </c>
+      <c r="B9" t="str">
+        <v>session-1770433763118</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E9" t="str">
+        <v>51.2</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-02-07T03:30:42.032Z</v>
+      </c>
+      <c r="B10" t="str">
+        <v>session-1770434998998</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E10" t="str">
+        <v>43.0</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-02-07T03:34:00.330Z</v>
+      </c>
+      <c r="B11" t="str">
+        <v>session-1770435127797</v>
+      </c>
+      <c r="C11" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E11" t="str">
+        <v>112.5</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-02-07T03:37:21.487Z</v>
+      </c>
+      <c r="B12" t="str">
+        <v>session-1770435271085</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E12" t="str">
+        <v>170.4</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>28</v>
+      </c>
+      <c r="J12">
+        <v>28</v>
+      </c>
+      <c r="K12" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-02-07T03:54:14.299Z</v>
+      </c>
+      <c r="B13" t="str">
+        <v>session-1770436254837</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E13" t="str">
+        <v>199.4</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>27</v>
+      </c>
+      <c r="J13">
+        <v>27</v>
+      </c>
+      <c r="K13" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-02-07T04:08:04.028Z</v>
+      </c>
+      <c r="B14" t="str">
+        <v>session-1770437207357</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E14" t="str">
+        <v>76.6</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-02-07T04:33:26.618Z</v>
+      </c>
+      <c r="B15" t="str">
+        <v>session-1770438629652</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E15" t="str">
+        <v>176.9</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>26</v>
+      </c>
+      <c r="J15">
+        <v>26</v>
+      </c>
+      <c r="K15" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-02-07T04:51:05.912Z</v>
+      </c>
+      <c r="B16" t="str">
+        <v>session-1770439669146</v>
+      </c>
+      <c r="C16" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E16" t="str">
+        <v>196.7</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>27</v>
+      </c>
+      <c r="J16">
+        <v>27</v>
+      </c>
+      <c r="K16" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-02-07T05:19:23.627Z</v>
+      </c>
+      <c r="B17" t="str">
+        <v>session-1770441518345</v>
+      </c>
+      <c r="C17" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E17" t="str">
+        <v>45.3</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-02-07T05:27:04.867Z</v>
+      </c>
+      <c r="B18" t="str">
+        <v>session-1770441983627</v>
+      </c>
+      <c r="C18" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E18" t="str">
+        <v>41.2</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-02-07T05:28:48.621Z</v>
+      </c>
+      <c r="B19" t="str">
+        <v>session-1770442080450</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E19" t="str">
+        <v>48.1</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-02-07T05:31:46.138Z</v>
+      </c>
+      <c r="B20" t="str">
+        <v>session-1770442257096</v>
+      </c>
+      <c r="C20" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E20" t="str">
+        <v>49.0</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-02-07T05:36:25.045Z</v>
+      </c>
+      <c r="B21" t="str">
+        <v>session-1770442405946</v>
+      </c>
+      <c r="C21" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E21" t="str">
+        <v>179.1</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>28</v>
+      </c>
+      <c r="J21">
+        <v>28</v>
+      </c>
+      <c r="K21" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-02-07T05:45:33.526Z</v>
+      </c>
+      <c r="B22" t="str">
+        <v>session-1770442953576</v>
+      </c>
+      <c r="C22" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E22" t="str">
+        <v>179.9</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>26</v>
+      </c>
+      <c r="J22">
+        <v>26</v>
+      </c>
+      <c r="K22" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-02-07T05:56:16.947Z</v>
+      </c>
+      <c r="B23" t="str">
+        <v>session-1770443590794</v>
+      </c>
+      <c r="C23" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E23" t="str">
+        <v>186.1</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>24</v>
+      </c>
+      <c r="J23">
+        <v>23</v>
+      </c>
+      <c r="K23" t="str">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-02-07T06:07:04.201Z</v>
+      </c>
+      <c r="B24" t="str">
+        <v>session-1770444195520</v>
+      </c>
+      <c r="C24" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E24" t="str">
+        <v>228.6</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>30</v>
+      </c>
+      <c r="J24">
+        <v>30</v>
+      </c>
+      <c r="K24" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-02-07T06:11:17.272Z</v>
+      </c>
+      <c r="B25" t="str">
+        <v>session-1770444625616</v>
+      </c>
+      <c r="C25" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E25" t="str">
+        <v>51.6</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-02-07T06:14:09.235Z</v>
+      </c>
+      <c r="B26" t="str">
+        <v>session-1770444800285</v>
+      </c>
+      <c r="C26" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E26" t="str">
+        <v>48.9</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-02-07T06:16:07.093Z</v>
+      </c>
+      <c r="B27" t="str">
+        <v>session-1770444911882</v>
+      </c>
+      <c r="C27" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E27" t="str">
+        <v>55.2</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-02-07T06:20:43.691Z</v>
+      </c>
+      <c r="B28" t="str">
+        <v>session-1770445119743</v>
+      </c>
+      <c r="C28" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E28" t="str">
+        <v>123.9</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-02-07T06:33:48.627Z</v>
+      </c>
+      <c r="B29" t="str">
+        <v>session-1770445846142</v>
+      </c>
+      <c r="C29" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E29" t="str">
+        <v>182.4</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>28</v>
+      </c>
+      <c r="J29">
+        <v>28</v>
+      </c>
+      <c r="K29" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-02-07T06:47:02.170Z</v>
+      </c>
+      <c r="B30" t="str">
+        <v>session-1770446641665</v>
+      </c>
+      <c r="C30" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E30" t="str">
+        <v>180.5</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>27</v>
+      </c>
+      <c r="J30">
+        <v>27</v>
+      </c>
+      <c r="K30" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-02-07T06:50:44.179Z</v>
+      </c>
+      <c r="B31" t="str">
+        <v>session-1770446915572</v>
+      </c>
+      <c r="C31" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E31" t="str">
+        <v>128.6</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-02-07T06:53:55.927Z</v>
+      </c>
+      <c r="B32" t="str">
+        <v>session-1770447054542</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E32" t="str">
+        <v>181.3</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>26</v>
+      </c>
+      <c r="J32">
+        <v>26</v>
+      </c>
+      <c r="K32" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-02-07T07:00:54.560Z</v>
+      </c>
+      <c r="B33" t="str">
+        <v>session-1770447389683</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E33" t="str">
+        <v>264.8</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>34</v>
+      </c>
+      <c r="J33">
+        <v>34</v>
+      </c>
+      <c r="K33" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-02-07T07:12:43.851Z</v>
+      </c>
+      <c r="B34" t="str">
+        <v>session-1770448188809</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E34" t="str">
+        <v>175.0</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>28</v>
+      </c>
+      <c r="J34">
+        <v>28</v>
+      </c>
+      <c r="K34" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-02-07T07:19:33.940Z</v>
+      </c>
+      <c r="B35" t="str">
+        <v>session-1770448590892</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E35" t="str">
+        <v>183.0</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>28</v>
+      </c>
+      <c r="J35">
+        <v>28</v>
+      </c>
+      <c r="K35" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-02-07T07:32:30.865Z</v>
+      </c>
+      <c r="B36" t="str">
+        <v>session-1770449352555</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E36" t="str">
+        <v>198.3</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>31</v>
+      </c>
+      <c r="J36">
+        <v>31</v>
+      </c>
+      <c r="K36" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-02-07T07:38:45.260Z</v>
+      </c>
+      <c r="B37" t="str">
+        <v>session-1770449674612</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E37" t="str">
+        <v>250.6</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>26</v>
+      </c>
+      <c r="J37">
+        <v>26</v>
+      </c>
+      <c r="K37" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-02-07T09:36:51.546Z</v>
+      </c>
+      <c r="B38" t="str">
+        <v>session-1770456744166</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E38" t="str">
+        <v>267.3</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>28</v>
+      </c>
+      <c r="J38">
+        <v>28</v>
+      </c>
+      <c r="K38" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-02-07T09:41:47.366Z</v>
+      </c>
+      <c r="B39" t="str">
+        <v>session-1770457027726</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E39" t="str">
+        <v>279.6</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>25</v>
+      </c>
+      <c r="J39">
+        <v>25</v>
+      </c>
+      <c r="K39" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-02-07T10:39:02.807Z</v>
+      </c>
+      <c r="B40" t="str">
+        <v>session-1770460643910</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E40" t="str">
+        <v>86.7</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-02-07T23:36:58.449Z</v>
+      </c>
+      <c r="B41" t="str">
+        <v>session-1770507190458</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E41" t="str">
+        <v>225.2</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>29</v>
+      </c>
+      <c r="J41">
+        <v>29</v>
+      </c>
+      <c r="K41" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-02-08T03:23:09.785Z</v>
+      </c>
+      <c r="B42" t="str">
+        <v>session-1770520775844</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E42" t="str">
+        <v>213.9</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42">
+        <v>5</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>26</v>
+      </c>
+      <c r="J42">
+        <v>26</v>
+      </c>
+      <c r="K42" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-02-08T04:22:03.097Z</v>
+      </c>
+      <c r="B43" t="str">
+        <v>session-1770524343381</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://www.crowd.live/FNJCN</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E43" t="str">
+        <v>179.6</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>26</v>
+      </c>
+      <c r="J43">
+        <v>26</v>
+      </c>
+      <c r="K43" t="str">
+        <v>100.0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K43"/>
   </ignoredErrors>
 </worksheet>
 </file>